--- a/data/gravel/Argonaut Supernaut GR3 2025.xlsx
+++ b/data/gravel/Argonaut Supernaut GR3 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18595866-11D2-1B4E-837C-FF176BE35E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF314454-EDAE-8E47-B2AF-2A320CA8BF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13380" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13540" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1480,6 +1480,7 @@
       <c r="A59" t="s">
         <v>55</v>
       </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">

--- a/data/gravel/Argonaut Supernaut GR3 2025.xlsx
+++ b/data/gravel/Argonaut Supernaut GR3 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF314454-EDAE-8E47-B2AF-2A320CA8BF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48632E0F-0FB9-FF47-8AB6-E8834EA39B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13540" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -317,6 +317,24 @@
   </si>
   <si>
     <t>Bend, Oregon, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -663,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1422,154 +1440,184 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53">
-        <v>48</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B59">
+        <v>48</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70">
-        <v>18000</v>
+        <v>60</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>97</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>98</v>
       </c>
     </row>

--- a/data/gravel/Argonaut Supernaut GR3 2025.xlsx
+++ b/data/gravel/Argonaut Supernaut GR3 2025.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48632E0F-0FB9-FF47-8AB6-E8834EA39B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE18D7C6-6C44-8847-9678-ED02CA361282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28640" yWindow="-22480" windowWidth="31340" windowHeight="20280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -335,6 +348,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>head.v</t>
+  </si>
+  <si>
+    <t>fork.v</t>
+  </si>
+  <si>
+    <t>fork angle</t>
+  </si>
+  <si>
+    <t>*argonaut has 526 for the 545 frame. See calc below</t>
   </si>
 </sst>
 </file>
@@ -681,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1028,7 +1053,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1045,7 +1070,7 @@
         <v>546</v>
       </c>
       <c r="F17">
-        <v>526</v>
+        <v>562</v>
       </c>
       <c r="G17">
         <v>571</v>
@@ -1059,8 +1084,11 @@
       <c r="J17">
         <v>635</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1092,7 +1120,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1124,7 +1152,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1156,7 +1184,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>93</v>
       </c>
@@ -1188,12 +1216,12 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1201,7 +1229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1209,7 +1237,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -1217,7 +1245,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1225,7 +1253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -1233,7 +1261,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -1262,7 +1290,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1291,7 +1319,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1320,7 +1348,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1328,7 +1356,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -1336,47 +1364,202 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>31</v>
       </c>
       <c r="B34" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34">
+        <f>D9 - ATAN(D19/D20)*180/PI()</f>
+        <v>60.288684688874845</v>
+      </c>
+      <c r="E34">
+        <f>E9 - ATAN(E19/E20)*180/PI()</f>
+        <v>60.288684688874845</v>
+      </c>
+      <c r="F34">
+        <f>F9 - ATAN(F19/F20)*180/PI()</f>
+        <v>60.288684688874845</v>
+      </c>
+      <c r="G34">
+        <f>G9 - ATAN(G19/G20)*180/PI()</f>
+        <v>60.288684688874845</v>
+      </c>
+      <c r="H34">
+        <f>H9 - ATAN(H19/H20)*180/PI()</f>
+        <v>60.288684688874845</v>
+      </c>
+      <c r="I34">
+        <f>I9 - ATAN(I19/I20)*180/PI()</f>
+        <v>60.288684688874845</v>
+      </c>
+      <c r="J34">
+        <f>J9 - ATAN(J19/J20)*180/PI()</f>
+        <v>60.288684688874845</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>69</v>
       </c>
       <c r="B35" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35">
+        <f>D20*SIN(D34*PI()/180)</f>
+        <v>343.07079161060665</v>
+      </c>
+      <c r="E35">
+        <f>E20*SIN(E34*PI()/180)</f>
+        <v>343.07079161060665</v>
+      </c>
+      <c r="F35">
+        <f>F20*SIN(F34*PI()/180)</f>
+        <v>343.07079161060665</v>
+      </c>
+      <c r="G35">
+        <f>G20*SIN(G34*PI()/180)</f>
+        <v>343.07079161060665</v>
+      </c>
+      <c r="H35">
+        <f>H20*SIN(H34*PI()/180)</f>
+        <v>343.07079161060665</v>
+      </c>
+      <c r="I35">
+        <f>I20*SIN(I34*PI()/180)</f>
+        <v>343.07079161060665</v>
+      </c>
+      <c r="J35">
+        <f>J20*SIN(J34*PI()/180)</f>
+        <v>343.07079161060665</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>71</v>
       </c>
       <c r="B36" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36">
+        <f>D16*SIN(D9*PI()/180)</f>
+        <v>102.3459324780227</v>
+      </c>
+      <c r="E36">
+        <f>E16*SIN(E9*PI()/180)</f>
+        <v>120.9542838376632</v>
+      </c>
+      <c r="F36">
+        <f>F16*SIN(F9*PI()/180)</f>
+        <v>139.56263519730368</v>
+      </c>
+      <c r="G36">
+        <f>G16*SIN(G9*PI()/180)</f>
+        <v>148.86681087712392</v>
+      </c>
+      <c r="H36">
+        <f>H16*SIN(H9*PI()/180)</f>
+        <v>158.17098655694417</v>
+      </c>
+      <c r="I36">
+        <f>I16*SIN(I9*PI()/180)</f>
+        <v>190.73560143631505</v>
+      </c>
+      <c r="J36">
+        <f>J16*SIN(J9*PI()/180)</f>
+        <v>213.99604063586565</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>73</v>
       </c>
       <c r="B37" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="1">
+        <f>D35+D36+D12 + 4.5</f>
+        <v>526.91672408862928</v>
+      </c>
+      <c r="E37" s="1">
+        <f>E35+E36+E12 + 4.5</f>
+        <v>545.52507544826983</v>
+      </c>
+      <c r="F37" s="1">
+        <f>F35+F36+F12 + 4.5</f>
+        <v>562.13342680791038</v>
+      </c>
+      <c r="G37" s="1">
+        <f>G35+G36+G12 + 4.5</f>
+        <v>571.4376024877306</v>
+      </c>
+      <c r="H37" s="1">
+        <f>H35+H36+H12 + 4.5</f>
+        <v>580.74177816755082</v>
+      </c>
+      <c r="I37" s="1">
+        <f>I35+I36+I12 + 4.5</f>
+        <v>611.3063930469217</v>
+      </c>
+      <c r="J37" s="1">
+        <f>J35+J36+J12 + 4.5</f>
+        <v>634.56683224647236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>33</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38">
+        <f>D17</f>
+        <v>527</v>
+      </c>
+      <c r="E38">
+        <f>E17</f>
+        <v>546</v>
+      </c>
+      <c r="F38">
+        <f>F17</f>
+        <v>562</v>
+      </c>
+      <c r="G38">
+        <f>G17</f>
+        <v>571</v>
+      </c>
+      <c r="H38">
+        <f>H17</f>
+        <v>581</v>
+      </c>
+      <c r="I38">
+        <f>I17</f>
+        <v>611</v>
+      </c>
+      <c r="J38">
+        <f>J17</f>
+        <v>635</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -1384,12 +1567,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -1397,32 +1580,32 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -1430,7 +1613,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>44</v>
       </c>
